--- a/high60/test/2026-10-08_high60_kr_daily.xlsx
+++ b/high60/test/2026-10-08_high60_kr_daily.xlsx
@@ -1544,7 +1544,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>뉴스: 대원미디어 '치이카와' 개봉 10일만에 100만 관객…먼작귀 IP 확장</t>
+          <t>뉴스: '귀여운 게 최고'…티니핑·치이카와에 캐릭터株 싱글벙글 |</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>핸드셋 업종 동반 신고가 3종목 · 뉴스: 파인엠텍, 폴더블 흥행에 실적 '껑충'…3분기 영업익 1066% 상승 전망</t>
+          <t>핸드셋 업종 동반 신고가 3종목 · 뉴스: [리포트 브리핑]파인엠텍, '이제부터 말보다 숫자로' 목표가 15,000원 - 메리츠증권</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>전기제품 업종 동반 신고가 9종목 · 뉴스: KCGI-K기술투자 중국계 피노에…1000억 투자한다</t>
+          <t>전기제품 업종 동반 신고가 9종목 · 뉴스: 피노, 유방암 인식의 달 맞아 ‘핑크 리본’ 캠페인 전개</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>자동차부품 업종 동반 신고가 4종목 · 뉴스: [MK 골든크로스 돌파종목 : 스톤브릿지벤처스(330730) &amp; 나래나노텍(137080)]</t>
+          <t>자동차부품 업종 동반 신고가 4종목 · 뉴스: 대형주 눈치보기 속 코스닥 선방…반도체 장비·이차전지로 수급 집중</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>반도체와반도체장비 업종 동반 신고가 20종목 · 뉴스: 티엘비, 3분기 영업이익 93% 급증 전망…서버용 메모리 수혜</t>
+          <t>반도체와반도체장비 업종 동반 신고가 20종목 · 뉴스: LG이노텍 10% 급락에 손절 나선 초고수...메모리 약세에 삼전닉스도 투매 [주식 초고수는 지금]</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네이버 업종 매핑 4074종목</t>
+          <t>네이버 업종 매핑 4089종목</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.0.1</t>
+          <t>1.0.2</t>
         </is>
       </c>
     </row>
